--- a/LubanConfig/DataTables/Datas/__enums__.xlsx
+++ b/LubanConfig/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87771E6-6458-43C8-A00A-4DDB59175485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>SUYANG KING</author>
+  </authors>
+  <commentList>
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{FEF3F7A8-4465-4BE8-A0A9-4975721CE1B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>SUYANG KING:
+Stenball is not finished.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -77,13 +103,66 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>Artifacts.ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireTrailDuration</t>
+  </si>
+  <si>
+    <t>FireTrailSize</t>
+  </si>
+  <si>
+    <t>FireTrailUptime</t>
+  </si>
+  <si>
+    <t>SplitCount</t>
+  </si>
+  <si>
+    <t>SplitSize</t>
+  </si>
+  <si>
+    <t>Splitfire</t>
+  </si>
+  <si>
+    <t>StenSpeed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IceSize</t>
+  </si>
+  <si>
+    <t>IceAtk</t>
+  </si>
+  <si>
+    <t>LightningSize</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightningFrequency</t>
+  </si>
+  <si>
+    <t>LightingReq</t>
+  </si>
+  <si>
+    <t>Invester</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Headhunter</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stargate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +175,36 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -141,7 +250,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -150,6 +259,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -428,8 +543,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -465,13 +580,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -529,6 +644,135 @@
       </c>
       <c r="L3" s="1"/>
     </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
@@ -536,5 +780,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/LubanConfig/DataTables/Datas/__enums__.xlsx
+++ b/LubanConfig/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87771E6-6458-43C8-A00A-4DDB59175485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487F7D31-16F9-4E1E-80BB-82E1617243FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -147,22 +147,43 @@
     <t>LightingReq</t>
   </si>
   <si>
-    <t>Invester</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Headhunter</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stargate</t>
+    <t>StartingGold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterDamage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TeleportPoint</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BumperPoint</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpinnerPoint</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwitchPoint</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamagerPoint</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldIncrease</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +226,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -250,7 +278,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -267,6 +295,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -544,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -766,11 +800,51 @@
       </c>
     </row>
     <row r="18" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J18">
         <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/DataTables/Datas/__enums__.xlsx
+++ b/LubanConfig/DataTables/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487F7D31-16F9-4E1E-80BB-82E1617243FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76292C3F-9D74-4F53-9FBF-2E0C6D1AB621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -176,6 +176,34 @@
   </si>
   <si>
     <t>GoldIncrease</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallSizeChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallSpeedChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraGold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallCritChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeathZone</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -194,6 +222,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -294,13 +323,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -578,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -614,13 +643,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -800,7 +829,7 @@
       </c>
     </row>
     <row r="18" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>34</v>
       </c>
       <c r="J18">
@@ -808,7 +837,7 @@
       </c>
     </row>
     <row r="19" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J19">
@@ -816,7 +845,7 @@
       </c>
     </row>
     <row r="20" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>36</v>
       </c>
       <c r="J20">
@@ -845,6 +874,62 @@
       </c>
       <c r="J23">
         <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J29">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
